--- a/data/Results_Scenarios_TESTING.xlsx
+++ b/data/Results_Scenarios_TESTING.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msalman\Desktop\OSMOSE ETs\Python work\INDECATE2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F66E14-507D-4A74-B83C-8D9F4A14EA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB29A810-3C5A-414D-AA2A-A643771A686C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="710" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Results_Scenarios_TESTING.xlsx
+++ b/data/Results_Scenarios_TESTING.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msalman\Desktop\OSMOSE ETs\Python work\INDECATE2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB29A810-3C5A-414D-AA2A-A643771A686C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F23BF84-2C99-4F66-B655-8BB3CF25B2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="710" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13148" tabRatio="710" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NG" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="92">
   <si>
     <t>Lines</t>
   </si>
@@ -316,6 +316,36 @@
   </si>
   <si>
     <t>THESE ARE JGDs SUMS: CAUTION</t>
+  </si>
+  <si>
+    <t>NGfur</t>
+  </si>
+  <si>
+    <t>NGfur_CC</t>
+  </si>
+  <si>
+    <t>NGOxyfur</t>
+  </si>
+  <si>
+    <t>NGOxyfur_CC</t>
+  </si>
+  <si>
+    <t>Hybfur</t>
+  </si>
+  <si>
+    <t>Hybfur_CC</t>
+  </si>
+  <si>
+    <t>ELfur_CC</t>
+  </si>
+  <si>
+    <t>H2fur</t>
+  </si>
+  <si>
+    <t>H2fur_CC</t>
+  </si>
+  <si>
+    <t>ELfur</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1793,7 +1823,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2305,7 +2335,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -2641,7 +2671,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -2977,7 +3007,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -3313,7 +3343,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -3649,7 +3679,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:T11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
     <col min="2" max="5" width="13.77734375" customWidth="1"/>
@@ -3681,7 +3711,7 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="B2" s="8">
         <v>237</v>
@@ -3710,7 +3740,7 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="B3" s="8">
         <v>272.49803277397262</v>
@@ -3733,7 +3763,7 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="B4" s="8">
         <v>240</v>
@@ -3786,7 +3816,7 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="B5" s="8">
         <v>255.55110777397263</v>
@@ -3809,7 +3839,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B6" s="8">
         <v>238.63913893835618</v>
@@ -3832,7 +3862,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="B7" s="8">
         <v>250.29343013698627</v>
@@ -3855,7 +3885,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B8" s="8">
         <v>273.88444520547944</v>
@@ -3878,7 +3908,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="B9" s="8">
         <v>281.40845479452054</v>
@@ -3901,7 +3931,7 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="B10" s="8">
         <v>359.21323972602738</v>
@@ -3924,7 +3954,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B11" s="9">
         <v>369.59616780821921</v>
@@ -3953,7 +3983,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" customWidth="1"/>
     <col min="2" max="4" width="9.21875" customWidth="1"/>
@@ -4248,7 +4278,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
@@ -4800,7 +4830,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -5336,7 +5366,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -5908,7 +5938,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -6456,7 +6486,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -7040,7 +7070,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -7516,7 +7546,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -8028,7 +8058,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
